--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487459_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487459_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.768</v>
+        <v>6.7623</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6782</v>
+        <v>5.5923</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0898</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="n">
         <v>3.9355</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7357</v>
+        <v>0.73</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2535</v>
+        <v>0.1676</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4822</v>
+        <v>0.5624</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0576</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6178</v>
+        <v>5.5436</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7705</v>
+        <v>4.8299</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.7137</v>
       </c>
       <c r="G3" t="n">
         <v>1.5819</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>0.582</v>
+        <v>0.5077</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1911</v>
+        <v>-0.1317</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7731</v>
+        <v>0.6395</v>
       </c>
       <c r="V3" t="n">
         <v>3.6498</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7116</v>
+        <v>2.6673</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4025</v>
+        <v>1.1978</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3091</v>
+        <v>1.4695</v>
       </c>
       <c r="G4" t="n">
         <v>0.763</v>
@@ -766,13 +766,13 @@
         <v>0.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1663</v>
+        <v>0.122</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4446</v>
+        <v>0.24</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2783</v>
+        <v>-0.1179</v>
       </c>
       <c r="V4" t="n">
         <v>0.9988</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1326</v>
+        <v>1.8856</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3639</v>
+        <v>-0.4316</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2313</v>
+        <v>2.3172</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8092</v>
+        <v>-1.2368</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0183</v>
+        <v>-0.2612</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8276</v>
+        <v>-0.9755</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6144</v>
+        <v>-1.2523</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7472</v>
+        <v>0.1429</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1327</v>
+        <v>-1.3952</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8052</v>
+        <v>0.0156</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7655</v>
+        <v>-0.4041</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9603</v>
+        <v>0.4197</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9585</v>
+        <v>1.7626</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9585</v>
+        <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1897</v>
+        <v>-0.1898</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2506</v>
+        <v>-0.3958</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4403</v>
+        <v>0.206</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8249</v>
+        <v>1.5495</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8249</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0132</v>
+        <v>1.0408</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2238</v>
+        <v>1.2186</v>
       </c>
       <c r="F6" t="n">
-        <v>2.237</v>
+        <v>-0.1778</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2368</v>
+        <v>0.8092</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2612</v>
+        <v>-0.0183</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9755</v>
+        <v>0.8276</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2523</v>
+        <v>1.6144</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1429</v>
+        <v>1.7472</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3952</v>
+        <v>-0.1327</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0156</v>
+        <v>-0.8052</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4041</v>
+        <v>-1.7655</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4197</v>
+        <v>0.9603</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0622</v>
+        <v>0.0979</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.188</v>
+        <v>-0.3958</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1258</v>
+        <v>0.4937</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5495</v>
+        <v>-1.8249</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3329</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. REY ARTIGAS</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4209</v>
+        <v>0.9977</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8402</v>
+        <v>-1.1259</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2612</v>
+        <v>2.1235</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2208</v>
+        <v>1.0587</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2872</v>
+        <v>1.5945</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0664</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.2327</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2721</v>
+        <v>0.9101</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2425</v>
+        <v>-0.6774</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7354000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5593</v>
+        <v>0.6843</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8239</v>
+        <v>0.1416</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>2.546</v>
+        <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1118</v>
+        <v>-0.4527</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2811</v>
+        <v>-0.3794</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3929</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1152</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>R. REY ARTIGAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1801</v>
+        <v>0.4793</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7564</v>
+        <v>-1.969</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9364</v>
+        <v>2.4483</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0587</v>
+        <v>-0.2208</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5945</v>
+        <v>-1.2872</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5358000000000001</v>
+        <v>1.0664</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2327</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9101</v>
+        <v>0.2721</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6774</v>
+        <v>0.2425</v>
       </c>
       <c r="M8" t="n">
-        <v>0.826</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6843</v>
+        <v>-1.5593</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1416</v>
+        <v>0.8239</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3709</v>
+        <v>2.546</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2703</v>
+        <v>0.1701</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0098</v>
+        <v>-0.4099</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2605</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.1152</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.668</v>
+        <v>-0.1679</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6205</v>
+        <v>-1.2541</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9525</v>
+        <v>1.0862</v>
       </c>
       <c r="G9" t="n">
         <v>0.7748</v>
@@ -1156,13 +1156,13 @@
         <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0683</v>
+        <v>-0.5683</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7722</v>
+        <v>-0.4058</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2961</v>
+        <v>-0.1625</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5495</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0657</v>
+        <v>-0.9634</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6118</v>
+        <v>-0.5094</v>
       </c>
       <c r="F10" t="n">
         <v>-0.454</v>
@@ -1234,10 +1234,10 @@
         <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2729</v>
+        <v>-0.1706</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.297</v>
+        <v>-0.1947</v>
       </c>
       <c r="U10" t="n">
         <v>0.0241</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2502</v>
+        <v>-2.4938</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2759</v>
+        <v>-1.7711</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0257</v>
+        <v>-0.7227</v>
       </c>
       <c r="G11" t="n">
         <v>0.4971</v>
@@ -1312,13 +1312,13 @@
         <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2735</v>
+        <v>1.0298</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.2029</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5754</v>
+        <v>0.8269</v>
       </c>
       <c r="V11" t="n">
         <v>-3.0415</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.8603</v>
+        <v>15.7515</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8865</v>
+        <v>5.7775</v>
       </c>
       <c r="F12" t="n">
-        <v>9.973700000000001</v>
+        <v>9.9739</v>
       </c>
       <c r="G12" t="n">
         <v>6.9739</v>
@@ -1390,22 +1390,22 @@
         <v>15.6677</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3852999999999995</v>
+        <v>1.2761</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.5936</v>
+        <v>-1.7026</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9789</v>
+        <v>2.978899999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3330000000000002</v>
       </c>
       <c r="W12" t="n">
-        <v>4.0277</v>
+        <v>4.027699999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.3608</v>
+        <v>-4.360799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3828</v>
+        <v>4.4704</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7856</v>
+        <v>0.6833</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5972</v>
+        <v>3.7871</v>
       </c>
       <c r="G13" t="n">
         <v>2.9737</v>
@@ -1468,13 +1468,13 @@
         <v>0.9792</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0774</v>
+        <v>0.165</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3694</v>
+        <v>-0.4717</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4468</v>
+        <v>0.6367</v>
       </c>
       <c r="V13" t="n">
         <v>1.3318</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. HERMIDA PEREZ</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1988</v>
+        <v>1.068</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8935999999999999</v>
+        <v>1.2257</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3052</v>
+        <v>-0.1577</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8748</v>
+        <v>0.5288</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4613</v>
+        <v>2.5444</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.5866</v>
+        <v>-2.0156</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5998</v>
+        <v>2.1298</v>
       </c>
       <c r="K14" t="n">
-        <v>5.6821</v>
+        <v>3.4943</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.0823</v>
+        <v>-1.3645</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.725</v>
+        <v>-1.601</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2207</v>
+        <v>-0.9499</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5043</v>
+        <v>-0.6511</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.3294</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.8962</v>
+        <v>-1.9585</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="S14" t="n">
-        <v>0.771</v>
+        <v>0.0265</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6981000000000001</v>
+        <v>-0.4376</v>
       </c>
       <c r="U14" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.464</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8825</v>
+        <v>1.492</v>
       </c>
       <c r="W14" t="n">
         <v>1.492</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>A. HERMIDA PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0588</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4304</v>
+        <v>0.1773</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3716</v>
+        <v>0.5218</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5288</v>
+        <v>1.8748</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5444</v>
+        <v>4.4613</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.0156</v>
+        <v>-2.5866</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1298</v>
+        <v>3.5998</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4943</v>
+        <v>5.6821</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3645</v>
+        <v>-2.0823</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.601</v>
+        <v>-1.725</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9499</v>
+        <v>-1.2207</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6511</v>
+        <v>-0.5043</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9792</v>
+        <v>-3.3294</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9585</v>
+        <v>-4.8962</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9792</v>
+        <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0173</v>
+        <v>0.2713</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2329</v>
+        <v>-0.0182</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2502</v>
+        <v>0.2895</v>
       </c>
       <c r="V15" t="n">
-        <v>1.492</v>
+        <v>1.8825</v>
       </c>
       <c r="W15" t="n">
         <v>1.492</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1718</v>
+        <v>-1.2031</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.7401</v>
+        <v>-1.6378</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5683</v>
+        <v>0.4347</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4221</v>
@@ -1702,13 +1702,13 @@
         <v>0.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1132</v>
+        <v>0.0819</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4576</v>
+        <v>-0.3552</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5708</v>
+        <v>0.4371</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2754</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.2545</v>
+        <v>-1.8404</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3074</v>
+        <v>0.409</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.9472</v>
+        <v>-2.2494</v>
       </c>
       <c r="G17" t="n">
         <v>-3.346</v>
@@ -1780,13 +1780,13 @@
         <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8877</v>
+        <v>-0.4736</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3904</v>
+        <v>-0.674</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4974</v>
+        <v>0.2004</v>
       </c>
       <c r="V17" t="n">
         <v>0.6083</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.1383</v>
+        <v>-4.6175</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4166</v>
+        <v>-2.1096</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7218</v>
+        <v>-2.5079</v>
       </c>
       <c r="G18" t="n">
         <v>-3.2986</v>
@@ -1858,13 +1858,13 @@
         <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0149</v>
+        <v>-0.494</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.594</v>
+        <v>-0.287</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4209</v>
+        <v>-0.207</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2166</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. SAMA PEREZ</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.4575</v>
+        <v>-5.7282</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.1345</v>
+        <v>-3.8708</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.323</v>
+        <v>-1.8574</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.9143</v>
+        <v>-0.3703</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.7119</v>
+        <v>1.1851</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2024</v>
+        <v>-1.5554</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8373</v>
+        <v>1.762</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0839</v>
+        <v>3.086</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7534</v>
+        <v>-1.3241</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.077</v>
+        <v>-2.1323</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.628</v>
+        <v>-1.9009</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.449</v>
+        <v>-0.2314</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7626</v>
+        <v>-2.9377</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4936</v>
+        <v>-0.2047</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6981000000000001</v>
+        <v>-0.7169</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7955</v>
+        <v>0.5123</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2742</v>
+        <v>-2.2154</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0576</v>
+        <v>-0.9988</v>
       </c>
       <c r="X19" t="n">
         <v>-1.2166</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>I. SAMA PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.4786</v>
+        <v>-7.0264</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.4848</v>
+        <v>-4.8509</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9938</v>
+        <v>-2.1756</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3703</v>
+        <v>-4.9143</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1851</v>
+        <v>-2.7119</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5554</v>
+        <v>-2.2024</v>
       </c>
       <c r="J20" t="n">
-        <v>1.762</v>
+        <v>-1.8373</v>
       </c>
       <c r="K20" t="n">
-        <v>3.086</v>
+        <v>-1.0839</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3241</v>
+        <v>-0.7534</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1323</v>
+        <v>-3.077</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9009</v>
+        <v>-1.628</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2314</v>
+        <v>-1.449</v>
       </c>
       <c r="P20" t="n">
+        <v>-1.7626</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-2.9377</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-3.917</v>
-      </c>
       <c r="R20" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9550999999999999</v>
+        <v>0.9247</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.331</v>
+        <v>-0.0182</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3758</v>
+        <v>0.9429</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2154</v>
+        <v>-1.2742</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.9988</v>
+        <v>-0.0576</v>
       </c>
       <c r="X20" t="n">
         <v>-1.2166</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-14.8603</v>
+        <v>-14.1781</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.973799999999999</v>
+        <v>-9.973800000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.886700000000001</v>
+        <v>-4.204400000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-6.974000000000002</v>
@@ -2083,7 +2083,7 @@
         <v>-2.4696</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.833800000000001</v>
+        <v>-7.8338</v>
       </c>
       <c r="Q21" t="n">
         <v>-15.6678</v>
@@ -2092,13 +2092,13 @@
         <v>7.8338</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3851999999999995</v>
+        <v>0.2970999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.9791</v>
+        <v>-2.9788</v>
       </c>
       <c r="U21" t="n">
-        <v>2.5937</v>
+        <v>3.2759</v>
       </c>
       <c r="V21" t="n">
         <v>0.3330000000000002</v>
